--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig6_score_loss_attribution_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig6_score_loss_attribution_data.xlsx
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41.33974768444622</v>
+        <v>41.41681147379304</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03515612691943239</v>
+        <v>0.03521212037016312</v>
       </c>
       <c r="D2" t="n">
-        <v>16.60322969443464</v>
+        <v>16.43044772371755</v>
       </c>
       <c r="E2" t="n">
-        <v>37.96056816630741</v>
+        <v>38.05070066216535</v>
       </c>
       <c r="F2" t="n">
-        <v>4.061298327892309</v>
+        <v>4.066828019953902</v>
       </c>
     </row>
     <row r="3">
@@ -657,19 +657,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>59.07107036181408</v>
+        <v>53.65194265533054</v>
       </c>
       <c r="C9" t="n">
-        <v>2.681618263979068</v>
+        <v>2.518752585440346</v>
       </c>
       <c r="D9" t="n">
-        <v>16.42751018454564</v>
+        <v>24.04455814518975</v>
       </c>
       <c r="E9" t="n">
-        <v>13.82089091631851</v>
+        <v>12.29565132949913</v>
       </c>
       <c r="F9" t="n">
-        <v>7.9989102733427</v>
+        <v>7.489095284540248</v>
       </c>
     </row>
     <row r="10">
@@ -701,19 +701,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20.51988033957265</v>
+        <v>20.39307571012689</v>
       </c>
       <c r="C11" t="n">
-        <v>1.931832180910172</v>
+        <v>1.928184542095992</v>
       </c>
       <c r="D11" t="n">
-        <v>27.6139271641598</v>
+        <v>27.95160910419212</v>
       </c>
       <c r="E11" t="n">
-        <v>15.9820432973418</v>
+        <v>15.91420617996805</v>
       </c>
       <c r="F11" t="n">
-        <v>33.95231701801558</v>
+        <v>33.81292446361694</v>
       </c>
     </row>
     <row r="12">
@@ -745,19 +745,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7.844607764889264</v>
+        <v>8.503105974442969</v>
       </c>
       <c r="C13" t="n">
-        <v>1.499948818024594</v>
+        <v>1.604095615290723</v>
       </c>
       <c r="D13" t="n">
-        <v>44.34638691640175</v>
+        <v>40.60583374133186</v>
       </c>
       <c r="E13" t="n">
-        <v>40.42542115377505</v>
+        <v>43.15154810797035</v>
       </c>
       <c r="F13" t="n">
-        <v>5.88363534690934</v>
+        <v>6.135416560964104</v>
       </c>
     </row>
     <row r="14">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8471814923427826</v>
+        <v>0.7983056370153144</v>
       </c>
       <c r="C4" t="n">
         <v>6.239817530140111</v>
@@ -1016,19 +1016,19 @@
         <v>31.21537960247638</v>
       </c>
       <c r="I4" t="n">
-        <v>6.972955360052134</v>
+        <v>12.93580971000326</v>
       </c>
       <c r="J4" t="n">
         <v>22.90648419680678</v>
       </c>
       <c r="K4" t="n">
-        <v>12.98468556533073</v>
+        <v>13.27794069729554</v>
       </c>
       <c r="L4" t="n">
         <v>2.052785923753666</v>
       </c>
       <c r="M4" t="n">
-        <v>13.8970348647768</v>
+        <v>11.81166503747149</v>
       </c>
       <c r="N4" t="n">
         <v>14.15770609318997</v>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.27675647831893e-15</v>
+        <v>1.443289932012704e-15</v>
       </c>
     </row>
     <row r="3">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.443289932012704e-15</v>
+        <v>1.332267629550188e-15</v>
       </c>
     </row>
     <row r="12">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.554312234475219e-15</v>
+        <v>1.387778780781446e-15</v>
       </c>
     </row>
     <row r="14">

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig6_score_loss_attribution_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig6_score_loss_attribution_data.xlsx
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-8fdd3599890f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -657,19 +657,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53.65194265533054</v>
+        <v>58.32321214114593</v>
       </c>
       <c r="C9" t="n">
-        <v>2.518752585440346</v>
+        <v>2.67773832914428</v>
       </c>
       <c r="D9" t="n">
-        <v>24.04455814518975</v>
+        <v>17.66388410677928</v>
       </c>
       <c r="E9" t="n">
-        <v>12.29565132949913</v>
+        <v>13.41573524602162</v>
       </c>
       <c r="F9" t="n">
-        <v>7.489095284540248</v>
+        <v>7.919430176908906</v>
       </c>
     </row>
     <row r="10">
@@ -1016,7 +1016,7 @@
         <v>31.21537960247638</v>
       </c>
       <c r="I4" t="n">
-        <v>12.93580971000326</v>
+        <v>7.83642880417074</v>
       </c>
       <c r="J4" t="n">
         <v>22.90648419680678</v>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.221245327087672e-15</v>
+        <v>1.110223024625157e-15</v>
       </c>
     </row>
     <row r="10">

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig6_score_loss_attribution_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig6_score_loss_attribution_data.xlsx
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-8fdd3599890f</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
